--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/126.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/126.xlsx
@@ -426,13 +426,13 @@
         <v>-3.148095413057151</v>
       </c>
       <c r="E2">
-        <v>-26.06159479256026</v>
+        <v>-20.68606014914408</v>
       </c>
       <c r="F2">
-        <v>-0.35343883863257</v>
+        <v>-1.743060776627061</v>
       </c>
       <c r="G2">
-        <v>-9.781344650791993</v>
+        <v>-9.359512288110569</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-3.340406516365587</v>
       </c>
       <c r="E3">
-        <v>-26.55207243717721</v>
+        <v>-20.52347438541102</v>
       </c>
       <c r="F3">
-        <v>-0.1068935052721588</v>
+        <v>-1.343723904187684</v>
       </c>
       <c r="G3">
-        <v>-10.00714533973279</v>
+        <v>-9.715512115182481</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-3.636640867354148</v>
       </c>
       <c r="E4">
-        <v>-25.54966165823925</v>
+        <v>-20.26167255633913</v>
       </c>
       <c r="F4">
-        <v>-0.1998172754159989</v>
+        <v>-0.7776772635675032</v>
       </c>
       <c r="G4">
-        <v>-9.730337228343117</v>
+        <v>-9.727092072816363</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.007010802793726</v>
       </c>
       <c r="E5">
-        <v>-25.22078546627137</v>
+        <v>-21.19726647148325</v>
       </c>
       <c r="F5">
-        <v>-0.2698930158558231</v>
+        <v>-0.9788114959064456</v>
       </c>
       <c r="G5">
-        <v>-10.06711805910755</v>
+        <v>-9.467648023702186</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.448349639415514</v>
       </c>
       <c r="E6">
-        <v>-28.81072581159269</v>
+        <v>-21.31760161640884</v>
       </c>
       <c r="F6">
-        <v>-0.6999573487346452</v>
+        <v>-1.001657868875656</v>
       </c>
       <c r="G6">
-        <v>-8.718197238398842</v>
+        <v>-9.760694966448582</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.941050431746003</v>
       </c>
       <c r="E7">
-        <v>-25.8668091814258</v>
+        <v>-22.65181244808736</v>
       </c>
       <c r="F7">
-        <v>-0.7371700975706074</v>
+        <v>-0.9603927467051986</v>
       </c>
       <c r="G7">
-        <v>-9.720281945550445</v>
+        <v>-10.38798248547226</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.466564281496718</v>
       </c>
       <c r="E8">
-        <v>-30.80865719188074</v>
+        <v>-22.74825001504987</v>
       </c>
       <c r="F8">
-        <v>-0.9913148734843014</v>
+        <v>-0.7499319257781366</v>
       </c>
       <c r="G8">
-        <v>-10.94173316159805</v>
+        <v>-9.354288188183752</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.994679540129567</v>
       </c>
       <c r="E9">
-        <v>-26.74927937051405</v>
+        <v>-24.7834481605556</v>
       </c>
       <c r="F9">
-        <v>-0.9142667646151137</v>
+        <v>-0.1492371618010611</v>
       </c>
       <c r="G9">
-        <v>-9.016700637340666</v>
+        <v>-9.524750229399016</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.507538801540287</v>
       </c>
       <c r="E10">
-        <v>-27.16642791597983</v>
+        <v>-24.39327056943326</v>
       </c>
       <c r="F10">
-        <v>-0.6602876621819797</v>
+        <v>0.309087753391669</v>
       </c>
       <c r="G10">
-        <v>-9.435632462781363</v>
+        <v>-10.34299674542279</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.984049871469251</v>
       </c>
       <c r="E11">
-        <v>-29.20952339281972</v>
+        <v>-23.85182471543801</v>
       </c>
       <c r="F11">
-        <v>-0.623011129056002</v>
+        <v>-0.07038486872857615</v>
       </c>
       <c r="G11">
-        <v>-8.959306028249632</v>
+        <v>-8.745548704107639</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-7.404969259323626</v>
       </c>
       <c r="E12">
-        <v>-32.14721643581635</v>
+        <v>-25.5876760014954</v>
       </c>
       <c r="F12">
-        <v>0.2516644966622045</v>
+        <v>0.5982343655432532</v>
       </c>
       <c r="G12">
-        <v>-8.629982789409715</v>
+        <v>-8.688454330644584</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.748071130611557</v>
       </c>
       <c r="E13">
-        <v>-31.53511822736878</v>
+        <v>-25.77737392875695</v>
       </c>
       <c r="F13">
-        <v>0.2753914241805907</v>
+        <v>0.6891004710585393</v>
       </c>
       <c r="G13">
-        <v>-9.576778452983017</v>
+        <v>-8.161350219187993</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.006535336804507</v>
       </c>
       <c r="E14">
-        <v>-31.35519280635456</v>
+        <v>-27.47995799210246</v>
       </c>
       <c r="F14">
-        <v>0.7336210771219988</v>
+        <v>1.293968550010919</v>
       </c>
       <c r="G14">
-        <v>-8.432029607650028</v>
+        <v>-8.977442870924095</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.177515138091433</v>
       </c>
       <c r="E15">
-        <v>-32.73681046870034</v>
+        <v>-26.8777049711004</v>
       </c>
       <c r="F15">
-        <v>1.287792242655646</v>
+        <v>1.209890915361575</v>
       </c>
       <c r="G15">
-        <v>-8.345023933406587</v>
+        <v>-9.036910411220473</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.264254298146042</v>
       </c>
       <c r="E16">
-        <v>-31.84998356093235</v>
+        <v>-29.48726732356197</v>
       </c>
       <c r="F16">
-        <v>1.484572575925474</v>
+        <v>1.353340955239171</v>
       </c>
       <c r="G16">
-        <v>-7.188774758149743</v>
+        <v>-7.637794109630726</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-8.270084773214803</v>
       </c>
       <c r="E17">
-        <v>-33.4754092642852</v>
+        <v>-30.6128208182811</v>
       </c>
       <c r="F17">
-        <v>1.55598944319043</v>
+        <v>2.368352787767849</v>
       </c>
       <c r="G17">
-        <v>-7.932648993006469</v>
+        <v>-7.33707027241416</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-8.213945568903371</v>
       </c>
       <c r="E18">
-        <v>-34.20665064600812</v>
+        <v>-29.6020413185236</v>
       </c>
       <c r="F18">
-        <v>2.309783898920313</v>
+        <v>2.179107284393886</v>
       </c>
       <c r="G18">
-        <v>-6.006809748670435</v>
+        <v>-7.260969678327799</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.115963768598714</v>
       </c>
       <c r="E19">
-        <v>-35.62892201740698</v>
+        <v>-31.2147955741244</v>
       </c>
       <c r="F19">
-        <v>3.109610731223765</v>
+        <v>2.737070715897549</v>
       </c>
       <c r="G19">
-        <v>-6.363327808543683</v>
+        <v>-7.57389874650782</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-7.995183629081207</v>
       </c>
       <c r="E20">
-        <v>-34.31414198491167</v>
+        <v>-32.50970456703606</v>
       </c>
       <c r="F20">
-        <v>2.242106282111594</v>
+        <v>3.13281661564579</v>
       </c>
       <c r="G20">
-        <v>-7.918445237058518</v>
+        <v>-6.274108222886976</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.862158227588416</v>
       </c>
       <c r="E21">
-        <v>-37.82179060104284</v>
+        <v>-34.6138377141113</v>
       </c>
       <c r="F21">
-        <v>2.811824247060982</v>
+        <v>3.605811089174697</v>
       </c>
       <c r="G21">
-        <v>-5.144462535013578</v>
+        <v>-6.831416038518157</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-7.735524953246037</v>
       </c>
       <c r="E22">
-        <v>-37.72719083009156</v>
+        <v>-34.20601728128108</v>
       </c>
       <c r="F22">
-        <v>2.085231720104229</v>
+        <v>3.33599194526523</v>
       </c>
       <c r="G22">
-        <v>-5.770427711901855</v>
+        <v>-6.875720374229349</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-7.625789338255024</v>
       </c>
       <c r="E23">
-        <v>-38.73839395740418</v>
+        <v>-35.82331930328257</v>
       </c>
       <c r="F23">
-        <v>2.649580207548671</v>
+        <v>4.047731844689788</v>
       </c>
       <c r="G23">
-        <v>-6.810746773590313</v>
+        <v>-6.276734631945637</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-7.536800631575193</v>
       </c>
       <c r="E24">
-        <v>-37.9820339535887</v>
+        <v>-36.2301055864929</v>
       </c>
       <c r="F24">
-        <v>3.230631895303161</v>
+        <v>4.078285347974645</v>
       </c>
       <c r="G24">
-        <v>-7.526874014932687</v>
+        <v>-6.0784433587614</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-7.460944743736064</v>
       </c>
       <c r="E25">
-        <v>-36.39380025764969</v>
+        <v>-36.06751774615417</v>
       </c>
       <c r="F25">
-        <v>3.664159632293088</v>
+        <v>4.649139833000674</v>
       </c>
       <c r="G25">
-        <v>-6.682144105776663</v>
+        <v>-5.598995779070992</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-7.399302859363147</v>
       </c>
       <c r="E26">
-        <v>-38.76748720273461</v>
+        <v>-35.65620238599411</v>
       </c>
       <c r="F26">
-        <v>3.666878334109076</v>
+        <v>4.59404843051009</v>
       </c>
       <c r="G26">
-        <v>-6.193864377134519</v>
+        <v>-6.194903453481782</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.347734538082154</v>
       </c>
       <c r="E27">
-        <v>-39.15955658161541</v>
+        <v>-38.18680388474804</v>
       </c>
       <c r="F27">
-        <v>4.035137346697624</v>
+        <v>4.438868708208853</v>
       </c>
       <c r="G27">
-        <v>-7.036683221249848</v>
+        <v>-5.327692422651682</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.298810959878629</v>
       </c>
       <c r="E28">
-        <v>-40.45638228155349</v>
+        <v>-38.20031843439904</v>
       </c>
       <c r="F28">
-        <v>4.225360323606892</v>
+        <v>5.027723616897715</v>
       </c>
       <c r="G28">
-        <v>-5.050512280157776</v>
+        <v>-5.454558945312241</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.239758413927597</v>
       </c>
       <c r="E29">
-        <v>-40.23562456339921</v>
+        <v>-37.43013654329452</v>
       </c>
       <c r="F29">
-        <v>3.72357345589148</v>
+        <v>4.841176934522072</v>
       </c>
       <c r="G29">
-        <v>-4.302964727661353</v>
+        <v>-5.156114288123717</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.169717081717945</v>
       </c>
       <c r="E30">
-        <v>-41.15890213035956</v>
+        <v>-39.19879196900106</v>
       </c>
       <c r="F30">
-        <v>4.268120648939402</v>
+        <v>4.769827993384145</v>
       </c>
       <c r="G30">
-        <v>-5.704929351600005</v>
+        <v>-4.73928541745116</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.08660483337384</v>
       </c>
       <c r="E31">
-        <v>-41.87530824123019</v>
+        <v>-38.85208811742137</v>
       </c>
       <c r="F31">
-        <v>3.726157962188215</v>
+        <v>3.912467731486657</v>
       </c>
       <c r="G31">
-        <v>-4.775976821934667</v>
+        <v>-4.6586604029884</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.98754467260482</v>
       </c>
       <c r="E32">
-        <v>-39.83093149869659</v>
+        <v>-39.2867092229307</v>
       </c>
       <c r="F32">
-        <v>3.624313503483626</v>
+        <v>4.29978416454401</v>
       </c>
       <c r="G32">
-        <v>-6.447647026602868</v>
+        <v>-4.762910045256144</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.866299140564166</v>
       </c>
       <c r="E33">
-        <v>-41.58060051883169</v>
+        <v>-38.23693937525571</v>
       </c>
       <c r="F33">
-        <v>2.897616602234121</v>
+        <v>4.020034552209784</v>
       </c>
       <c r="G33">
-        <v>-6.284337120194959</v>
+        <v>-4.571226566632016</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.727495375476247</v>
       </c>
       <c r="E34">
-        <v>-39.16613526835394</v>
+        <v>-38.73961500153369</v>
       </c>
       <c r="F34">
-        <v>3.015552926105492</v>
+        <v>3.660089034875731</v>
       </c>
       <c r="G34">
-        <v>-4.563564031257099</v>
+        <v>-4.052568213927677</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.57446256551943</v>
       </c>
       <c r="E35">
-        <v>-39.68781806625999</v>
+        <v>-38.68433160558889</v>
       </c>
       <c r="F35">
-        <v>2.99271483681031</v>
+        <v>3.78153100959575</v>
       </c>
       <c r="G35">
-        <v>-4.207800476570682</v>
+        <v>-3.995784519070964</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.408716826533378</v>
       </c>
       <c r="E36">
-        <v>-40.41225441122718</v>
+        <v>-38.47645299575291</v>
       </c>
       <c r="F36">
-        <v>2.900567246922893</v>
+        <v>3.664502576397847</v>
       </c>
       <c r="G36">
-        <v>-4.553356019905846</v>
+        <v>-3.025107069350453</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.22680774793711</v>
       </c>
       <c r="E37">
-        <v>-42.2521394877602</v>
+        <v>-38.56612082825596</v>
       </c>
       <c r="F37">
-        <v>1.656675844265905</v>
+        <v>2.962116601685702</v>
       </c>
       <c r="G37">
-        <v>-2.862622158233335</v>
+        <v>-3.131581066009826</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.03241468346686</v>
       </c>
       <c r="E38">
-        <v>-39.64990755328696</v>
+        <v>-38.83617301162462</v>
       </c>
       <c r="F38">
-        <v>1.529488313240069</v>
+        <v>2.712272709327343</v>
       </c>
       <c r="G38">
-        <v>-2.715295230212222</v>
+        <v>-2.000609119884142</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.826837845868993</v>
       </c>
       <c r="E39">
-        <v>-38.12789058210535</v>
+        <v>-37.36502664935518</v>
       </c>
       <c r="F39">
-        <v>2.582797227534974</v>
+        <v>2.569268331112453</v>
       </c>
       <c r="G39">
-        <v>-3.209535288755878</v>
+        <v>-1.698846206320312</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.608991520544858</v>
       </c>
       <c r="E40">
-        <v>-37.22420163635856</v>
+        <v>-37.25930250187034</v>
       </c>
       <c r="F40">
-        <v>2.191024177850559</v>
+        <v>2.656253535345623</v>
       </c>
       <c r="G40">
-        <v>-1.734054707876066</v>
+        <v>-1.200173103460946</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.374499558308735</v>
       </c>
       <c r="E41">
-        <v>-37.96353139713658</v>
+        <v>-36.49956593724777</v>
       </c>
       <c r="F41">
-        <v>1.090070884016237</v>
+        <v>1.92024247101904</v>
       </c>
       <c r="G41">
-        <v>-3.574285026324906</v>
+        <v>-0.5048743824664736</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.126019052817611</v>
       </c>
       <c r="E42">
-        <v>-37.45552720072886</v>
+        <v>-37.2188564533835</v>
       </c>
       <c r="F42">
-        <v>0.6894425867958955</v>
+        <v>2.025552818936941</v>
       </c>
       <c r="G42">
-        <v>-3.121542753056995</v>
+        <v>-1.115522320838689</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.864951021778115</v>
       </c>
       <c r="E43">
-        <v>-37.29396728019303</v>
+        <v>-37.32481318070253</v>
       </c>
       <c r="F43">
-        <v>0.06524538286659251</v>
+        <v>1.85741743045592</v>
       </c>
       <c r="G43">
-        <v>-2.892055692753547</v>
+        <v>-0.4867036001123252</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.590706468695791</v>
       </c>
       <c r="E44">
-        <v>-37.29067170700678</v>
+        <v>-35.52446252277056</v>
       </c>
       <c r="F44">
-        <v>1.402655323462631</v>
+        <v>1.557710790653448</v>
       </c>
       <c r="G44">
-        <v>-0.8911079372757731</v>
+        <v>-0.03048642579364292</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.300726478937408</v>
       </c>
       <c r="E45">
-        <v>-37.12470730586097</v>
+        <v>-35.54625857580326</v>
       </c>
       <c r="F45">
-        <v>0.6549352858974765</v>
+        <v>1.084582121605288</v>
       </c>
       <c r="G45">
-        <v>-0.9358926499917304</v>
+        <v>0.1081858839079304</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.998872245808038</v>
       </c>
       <c r="E46">
-        <v>-35.46259213366459</v>
+        <v>-35.91802498112263</v>
       </c>
       <c r="F46">
-        <v>1.209821332499739</v>
+        <v>1.454022386110228</v>
       </c>
       <c r="G46">
-        <v>-0.6604434311617321</v>
+        <v>0.005831642213334003</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.688317024569956</v>
       </c>
       <c r="E47">
-        <v>-33.50958811688287</v>
+        <v>-35.17773998173989</v>
       </c>
       <c r="F47">
-        <v>1.776220857633513</v>
+        <v>1.272361414676296</v>
       </c>
       <c r="G47">
-        <v>-1.03677704248153</v>
+        <v>0.2168241878333364</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.371066698838767</v>
       </c>
       <c r="E48">
-        <v>-36.1303350674422</v>
+        <v>-35.76832455552485</v>
       </c>
       <c r="F48">
-        <v>1.093159037693874</v>
+        <v>1.000830863712647</v>
       </c>
       <c r="G48">
-        <v>0.03879229267613923</v>
+        <v>0.3520868650989157</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.048035126843363</v>
       </c>
       <c r="E49">
-        <v>-36.49113284165271</v>
+        <v>-34.87693326851088</v>
       </c>
       <c r="F49">
-        <v>0.9976549030903132</v>
+        <v>0.8410487321214555</v>
       </c>
       <c r="G49">
-        <v>-1.488310541003755</v>
+        <v>0.4454105412528513</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.726065404673791</v>
       </c>
       <c r="E50">
-        <v>-34.07089670403911</v>
+        <v>-33.91898469341086</v>
       </c>
       <c r="F50">
-        <v>0.7888185106401411</v>
+        <v>0.5324164335538185</v>
       </c>
       <c r="G50">
-        <v>-2.091891193767827</v>
+        <v>1.256634154326527</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.411720651601155</v>
       </c>
       <c r="E51">
-        <v>-33.86522552602228</v>
+        <v>-33.77011491007804</v>
       </c>
       <c r="F51">
-        <v>0.9741740006905585</v>
+        <v>1.246410320681393</v>
       </c>
       <c r="G51">
-        <v>-0.3927246270660202</v>
+        <v>1.427045286022264</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.110209976419389</v>
       </c>
       <c r="E52">
-        <v>-34.93850047319013</v>
+        <v>-33.85188541124693</v>
       </c>
       <c r="F52">
-        <v>0.9050185764352445</v>
+        <v>0.6476862427555781</v>
       </c>
       <c r="G52">
-        <v>-0.7487127057872722</v>
+        <v>1.313689366620717</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.825381608000059</v>
       </c>
       <c r="E53">
-        <v>-34.3358591269292</v>
+        <v>-32.80281330307452</v>
       </c>
       <c r="F53">
-        <v>1.480460560137977</v>
+        <v>0.5929203886542944</v>
       </c>
       <c r="G53">
-        <v>0.529058797952121</v>
+        <v>0.9357971407800242</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.564511440964215</v>
       </c>
       <c r="E54">
-        <v>-33.83292600154908</v>
+        <v>-31.98312928618936</v>
       </c>
       <c r="F54">
-        <v>0.09196934364830736</v>
+        <v>0.5413851674239287</v>
       </c>
       <c r="G54">
-        <v>0.0285660061127485</v>
+        <v>1.322411864299626</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.334084206524895</v>
       </c>
       <c r="E55">
-        <v>-29.79569310296638</v>
+        <v>-32.70588150396434</v>
       </c>
       <c r="F55">
-        <v>-0.05855743895140481</v>
+        <v>0.3035144975056339</v>
       </c>
       <c r="G55">
-        <v>-2.412435803920125</v>
+        <v>0.6523877616917214</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.1374346430883</v>
       </c>
       <c r="E56">
-        <v>-30.9762434220489</v>
+        <v>-31.07897102756287</v>
       </c>
       <c r="F56">
-        <v>0.3684974351530467</v>
+        <v>0.1220440505743462</v>
       </c>
       <c r="G56">
-        <v>-0.3457729963394389</v>
+        <v>0.5638730770746166</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-0.9752232697258315</v>
       </c>
       <c r="E57">
-        <v>-31.20825218968213</v>
+        <v>-32.45622366480625</v>
       </c>
       <c r="F57">
-        <v>0.4348670598327459</v>
+        <v>0.5235752682637393</v>
       </c>
       <c r="G57">
-        <v>-2.178969968859819</v>
+        <v>1.091436679579243</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-0.849197298345585</v>
       </c>
       <c r="E58">
-        <v>-31.73683970141571</v>
+        <v>-30.6750982220969</v>
       </c>
       <c r="F58">
-        <v>1.550469202818175</v>
+        <v>0.0873702478279645</v>
       </c>
       <c r="G58">
-        <v>-1.762830334759317</v>
+        <v>0.186278476117311</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-0.7603953077200689</v>
       </c>
       <c r="E59">
-        <v>-30.17395928400911</v>
+        <v>-29.56322748208742</v>
       </c>
       <c r="F59">
-        <v>-0.38169113727245</v>
+        <v>0.03724656465196922</v>
       </c>
       <c r="G59">
-        <v>-1.657959335278888</v>
+        <v>0.8118677057844677</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-0.7070812982521708</v>
       </c>
       <c r="E60">
-        <v>-29.54592312710252</v>
+        <v>-28.3270241312522</v>
       </c>
       <c r="F60">
-        <v>-0.7050170168309445</v>
+        <v>0.3081334741436439</v>
       </c>
       <c r="G60">
-        <v>-4.36371936504115</v>
+        <v>0.3390984107581271</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-0.6853351763914443</v>
       </c>
       <c r="E61">
-        <v>-30.81564704654042</v>
+        <v>-30.25163887202305</v>
       </c>
       <c r="F61">
-        <v>0.5893534386178397</v>
+        <v>0.03068672318919993</v>
       </c>
       <c r="G61">
-        <v>-2.8468271534571</v>
+        <v>-0.5105605841859183</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-0.6916436830941728</v>
       </c>
       <c r="E62">
-        <v>-28.29610139633319</v>
+        <v>-28.90727966847231</v>
       </c>
       <c r="F62">
-        <v>0.08812157706230365</v>
+        <v>0.1300527066246118</v>
       </c>
       <c r="G62">
-        <v>-3.118932008465882</v>
+        <v>-0.3784386326634483</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-0.7215301936321413</v>
       </c>
       <c r="E63">
-        <v>-28.53172138121336</v>
+        <v>-28.87120487490485</v>
       </c>
       <c r="F63">
-        <v>-0.5095910642646936</v>
+        <v>-0.2330207260224115</v>
       </c>
       <c r="G63">
-        <v>-3.580185309100822</v>
+        <v>-0.2113353143646513</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-0.7676222587394892</v>
       </c>
       <c r="E64">
-        <v>-30.77829098727926</v>
+        <v>-28.13349071333218</v>
       </c>
       <c r="F64">
-        <v>-0.03239262616657962</v>
+        <v>-0.3679129022616858</v>
       </c>
       <c r="G64">
-        <v>-4.435251156093063</v>
+        <v>-1.553378128448071</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.8207076996557177</v>
       </c>
       <c r="E65">
-        <v>-28.85504265303428</v>
+        <v>-28.41061373898136</v>
       </c>
       <c r="F65">
-        <v>-0.1290109149269056</v>
+        <v>-0.1844237239697757</v>
       </c>
       <c r="G65">
-        <v>-3.36410442227274</v>
+        <v>-2.00109732912268</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.8715804999878319</v>
       </c>
       <c r="E66">
-        <v>-27.26378749585646</v>
+        <v>-26.72170204731719</v>
       </c>
       <c r="F66">
-        <v>-0.7330738207637638</v>
+        <v>-0.4935812074707876</v>
       </c>
       <c r="G66">
-        <v>-2.125204294750432</v>
+        <v>-2.514437595094921</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-0.9107857700051692</v>
       </c>
       <c r="E67">
-        <v>-26.00906912893516</v>
+        <v>-26.77643306615578</v>
       </c>
       <c r="F67">
-        <v>-1.760272594522429</v>
+        <v>-0.4582985546833482</v>
       </c>
       <c r="G67">
-        <v>-3.96744749727902</v>
+        <v>-2.161305670956347</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-0.9289363049384151</v>
       </c>
       <c r="E68">
-        <v>-27.82585404407948</v>
+        <v>-27.67499694912773</v>
       </c>
       <c r="F68">
-        <v>-0.5347560375943398</v>
+        <v>-0.9237200934158617</v>
       </c>
       <c r="G68">
-        <v>-5.134800169281868</v>
+        <v>-2.304520676246457</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.9177454860283226</v>
       </c>
       <c r="E69">
-        <v>-26.52530914340002</v>
+        <v>-26.87763021329655</v>
       </c>
       <c r="F69">
-        <v>-1.305149319341519</v>
+        <v>-1.06562025788282</v>
       </c>
       <c r="G69">
-        <v>-4.081166310178732</v>
+        <v>-3.071886390934021</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-0.8717940079572871</v>
       </c>
       <c r="E70">
-        <v>-27.78789784578187</v>
+        <v>-26.36839251312535</v>
       </c>
       <c r="F70">
-        <v>-1.109227174700991</v>
+        <v>-0.8621351188547324</v>
       </c>
       <c r="G70">
-        <v>-3.554344159137983</v>
+        <v>-3.465312547091837</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-0.7871072450847335</v>
       </c>
       <c r="E71">
-        <v>-27.62482200311248</v>
+        <v>-25.56391132629473</v>
       </c>
       <c r="F71">
-        <v>-0.9113318589069951</v>
+        <v>-1.499185271405873</v>
       </c>
       <c r="G71">
-        <v>-3.335323573900307</v>
+        <v>-3.494874008097013</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-0.6619172371645164</v>
       </c>
       <c r="E72">
-        <v>-29.33143468144307</v>
+        <v>-27.19762268624061</v>
       </c>
       <c r="F72">
-        <v>-1.984840512319167</v>
+        <v>-1.632276576911461</v>
       </c>
       <c r="G72">
-        <v>-3.633355733443435</v>
+        <v>-3.242213978802842</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-0.4970095054361245</v>
       </c>
       <c r="E73">
-        <v>-29.02089907068564</v>
+        <v>-26.76655257641401</v>
       </c>
       <c r="F73">
-        <v>-1.624624118844399</v>
+        <v>-1.433330062883312</v>
       </c>
       <c r="G73">
-        <v>-3.202308747727676</v>
+        <v>-2.22831304163186</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-0.2963580164608882</v>
       </c>
       <c r="E74">
-        <v>-29.52086472657416</v>
+        <v>-26.69089352570961</v>
       </c>
       <c r="F74">
-        <v>-1.295782969118065</v>
+        <v>-2.213609909582904</v>
       </c>
       <c r="G74">
-        <v>-2.767883458511017</v>
+        <v>-2.748584834493507</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.06322817513899272</v>
       </c>
       <c r="E75">
-        <v>-26.03848217153759</v>
+        <v>-26.77835184978785</v>
       </c>
       <c r="F75">
-        <v>-2.1485706429521</v>
+        <v>-1.746288096028368</v>
       </c>
       <c r="G75">
-        <v>-3.603715950100526</v>
+        <v>-2.294516302973311</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>0.1980566685732716</v>
       </c>
       <c r="E76">
-        <v>-30.32266916870593</v>
+        <v>-25.12122883760391</v>
       </c>
       <c r="F76">
-        <v>-2.012409407851737</v>
+        <v>-2.012267757025858</v>
       </c>
       <c r="G76">
-        <v>-3.985602615165622</v>
+        <v>-2.946223421529965</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>0.4822004495051089</v>
       </c>
       <c r="E77">
-        <v>-28.20971875398808</v>
+        <v>-25.86970812293054</v>
       </c>
       <c r="F77">
-        <v>-2.299674797631563</v>
+        <v>-2.324457065221116</v>
       </c>
       <c r="G77">
-        <v>-3.869714273510694</v>
+        <v>-1.42266075751562</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>0.7811851450435761</v>
       </c>
       <c r="E78">
-        <v>-28.15794066840144</v>
+        <v>-28.08289006315613</v>
       </c>
       <c r="F78">
-        <v>-2.438258179017712</v>
+        <v>-2.365199487560407</v>
       </c>
       <c r="G78">
-        <v>-2.827285730192617</v>
+        <v>-1.208255968715033</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>1.089587893888535</v>
       </c>
       <c r="E79">
-        <v>-28.66904523706316</v>
+        <v>-26.23097105680942</v>
       </c>
       <c r="F79">
-        <v>-2.376196893199974</v>
+        <v>-2.169139833931015</v>
       </c>
       <c r="G79">
-        <v>-3.043750396475593</v>
+        <v>-1.034537023622355</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>1.401059575267184</v>
       </c>
       <c r="E80">
-        <v>-28.71882355139689</v>
+        <v>-30.01322792913259</v>
       </c>
       <c r="F80">
-        <v>-2.494561483018592</v>
+        <v>-2.9137915986362</v>
       </c>
       <c r="G80">
-        <v>-1.029631434535653</v>
+        <v>-1.573796761895168</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>1.708620371439151</v>
       </c>
       <c r="E81">
-        <v>-32.48419346647331</v>
+        <v>-28.00867425338711</v>
       </c>
       <c r="F81">
-        <v>-1.989900180415466</v>
+        <v>-2.700392558531408</v>
       </c>
       <c r="G81">
-        <v>-0.7413895672091995</v>
+        <v>-0.8518841105388871</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>2.002895912294603</v>
       </c>
       <c r="E82">
-        <v>-32.70250286655159</v>
+        <v>-30.64716787593743</v>
       </c>
       <c r="F82">
-        <v>-3.212063506097023</v>
+        <v>-2.403552069942622</v>
       </c>
       <c r="G82">
-        <v>-1.445632699172826</v>
+        <v>-0.2090952955054761</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>2.277579429898986</v>
       </c>
       <c r="E83">
-        <v>-31.88317394923472</v>
+        <v>-31.69324136553332</v>
       </c>
       <c r="F83">
-        <v>-2.933093387488831</v>
+        <v>-2.46308932028403</v>
       </c>
       <c r="G83">
-        <v>1.40201346688267</v>
+        <v>-0.8220276353949155</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>2.526347677278185</v>
       </c>
       <c r="E84">
-        <v>-33.35848805906862</v>
+        <v>-30.41631993086948</v>
       </c>
       <c r="F84">
-        <v>-2.603080097887536</v>
+        <v>-2.449604327333857</v>
       </c>
       <c r="G84">
-        <v>0.7176981483830114</v>
+        <v>-0.4903847499857949</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>2.743223774917191</v>
       </c>
       <c r="E85">
-        <v>-33.94057308587732</v>
+        <v>-33.06375126419084</v>
       </c>
       <c r="F85">
-        <v>-3.471951353214326</v>
+        <v>-2.851436242390467</v>
       </c>
       <c r="G85">
-        <v>0.4867569033423124</v>
+        <v>0.2187561388307603</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>2.921025265632904</v>
       </c>
       <c r="E86">
-        <v>-33.63774583533877</v>
+        <v>-34.48504455432271</v>
       </c>
       <c r="F86">
-        <v>-3.383463490512477</v>
+        <v>-2.831733523714881</v>
       </c>
       <c r="G86">
-        <v>0.7091818995267999</v>
+        <v>0.5659433975353695</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>3.054897272726052</v>
       </c>
       <c r="E87">
-        <v>-36.25569975128215</v>
+        <v>-34.83451859785606</v>
       </c>
       <c r="F87">
-        <v>-2.854583210153702</v>
+        <v>-2.087079273907487</v>
       </c>
       <c r="G87">
-        <v>-0.3018315541264112</v>
+        <v>-0.1771006205413828</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>3.138871245014168</v>
       </c>
       <c r="E88">
-        <v>-36.03384973854945</v>
+        <v>-37.03971806591534</v>
       </c>
       <c r="F88">
-        <v>-2.24530241804661</v>
+        <v>-2.196752632935933</v>
       </c>
       <c r="G88">
-        <v>0.2257424913565794</v>
+        <v>0.002077391491313098</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>3.166856609927918</v>
       </c>
       <c r="E89">
-        <v>-39.36884520669617</v>
+        <v>-38.67041834765072</v>
       </c>
       <c r="F89">
-        <v>-3.208602587088127</v>
+        <v>-2.823434939073635</v>
       </c>
       <c r="G89">
-        <v>2.118989200217156</v>
+        <v>-0.1053939096018653</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>3.133466727028098</v>
       </c>
       <c r="E90">
-        <v>-40.28569567913134</v>
+        <v>-38.88649539664191</v>
       </c>
       <c r="F90">
-        <v>-2.63365928056188</v>
+        <v>-2.686731951691841</v>
       </c>
       <c r="G90">
-        <v>-0.03809152478755592</v>
+        <v>-0.05314246735532401</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>3.036196651647135</v>
       </c>
       <c r="E91">
-        <v>-42.94924562560436</v>
+        <v>-41.61047456789118</v>
       </c>
       <c r="F91">
-        <v>-3.122987502539187</v>
+        <v>-2.575241154581653</v>
       </c>
       <c r="G91">
-        <v>-0.3849968230763249</v>
+        <v>-0.2190683398435289</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>2.873579287467161</v>
       </c>
       <c r="E92">
-        <v>-43.87476177346879</v>
+        <v>-43.62924468600155</v>
       </c>
       <c r="F92">
-        <v>-2.20898679110788</v>
+        <v>-1.851037639214574</v>
       </c>
       <c r="G92">
-        <v>-0.3834956449364347</v>
+        <v>-1.046073903970484</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>2.645838122057159</v>
       </c>
       <c r="E93">
-        <v>-44.26406719021292</v>
+        <v>-44.84824543552933</v>
       </c>
       <c r="F93">
-        <v>-2.716370108996605</v>
+        <v>-1.723899810232906</v>
       </c>
       <c r="G93">
-        <v>-0.9837006049441969</v>
+        <v>-0.3380399708605613</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>2.356393963221198</v>
       </c>
       <c r="E94">
-        <v>-44.53579519435115</v>
+        <v>-44.99409168101766</v>
       </c>
       <c r="F94">
-        <v>-3.476605121283254</v>
+        <v>-1.838595560824525</v>
       </c>
       <c r="G94">
-        <v>0.9303406845845974</v>
+        <v>-1.954495538171308</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>2.012524127916134</v>
       </c>
       <c r="E95">
-        <v>-47.38544015726142</v>
+        <v>-48.35644019894971</v>
       </c>
       <c r="F95">
-        <v>-2.560989093416487</v>
+        <v>-1.67594479291744</v>
       </c>
       <c r="G95">
-        <v>-1.870541824354878</v>
+        <v>-2.430332458092206</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>1.618019816134113</v>
       </c>
       <c r="E96">
-        <v>-49.79565978746236</v>
+        <v>-49.91740702423839</v>
       </c>
       <c r="F96">
-        <v>-3.253944933615163</v>
+        <v>-0.7484980218038906</v>
       </c>
       <c r="G96">
-        <v>-1.089735996512263</v>
+        <v>-2.215721420468921</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>1.185678455669478</v>
       </c>
       <c r="E97">
-        <v>-51.88493274441736</v>
+        <v>-51.97455489159584</v>
       </c>
       <c r="F97">
-        <v>-2.352286896485569</v>
+        <v>-0.8609836881648411</v>
       </c>
       <c r="G97">
-        <v>-1.831498138994779</v>
+        <v>-2.533138358601065</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>0.7157239966053819</v>
       </c>
       <c r="E98">
-        <v>-52.75254793489952</v>
+        <v>-53.50140308585105</v>
       </c>
       <c r="F98">
-        <v>-2.003986568100072</v>
+        <v>-0.2642104154726185</v>
       </c>
       <c r="G98">
-        <v>-2.557316464259365</v>
+        <v>-2.621141337278312</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>0.233410556639979</v>
       </c>
       <c r="E99">
-        <v>-55.86876780499674</v>
+        <v>-56.87836104376959</v>
       </c>
       <c r="F99">
-        <v>-2.599144524356835</v>
+        <v>-0.02754584849279971</v>
       </c>
       <c r="G99">
-        <v>-2.46017065802404</v>
+        <v>-3.642174828672216</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.2734538713345371</v>
       </c>
       <c r="E100">
-        <v>-57.04659257914734</v>
+        <v>-58.70411923155691</v>
       </c>
       <c r="F100">
-        <v>-2.115679486856543</v>
+        <v>0.2857874350857245</v>
       </c>
       <c r="G100">
-        <v>-3.87995361379704</v>
+        <v>-4.478667838643277</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.7599067318500927</v>
       </c>
       <c r="E101">
-        <v>-59.26222491405458</v>
+        <v>-59.236769622269</v>
       </c>
       <c r="F101">
-        <v>-1.41433891180673</v>
+        <v>1.022037069224314</v>
       </c>
       <c r="G101">
-        <v>-3.858623830487645</v>
+        <v>-5.299185702461316</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-1.27586855315376</v>
       </c>
       <c r="E102">
-        <v>-60.43252147352751</v>
+        <v>-61.13119025713263</v>
       </c>
       <c r="F102">
-        <v>-1.317465485886342</v>
+        <v>0.7974534124469231</v>
       </c>
       <c r="G102">
-        <v>-3.821384169640005</v>
+        <v>-5.774179351879285</v>
       </c>
     </row>
   </sheetData>
